--- a/Paper1/data/Table4_sensitivity.xlsx
+++ b/Paper1/data/Table4_sensitivity.xlsx
@@ -468,12 +468,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4 significant hotspots</t>
+          <t>0 significant hotspots</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fixed distance-band (55 km)</t>
+          <t>Fixed distance-band (0.5deg)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>I=0.0891, p=0.058</t>
+          <t>I=0.030, p=0.226</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -505,7 +505,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I=-0.0646, p=0.408</t>
+          <t>I=-0.102, p=0.268</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>I=0.0009, p=0.073</t>
+          <t>I=-0.015, p=0.197</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I=0.0891, p=0.058</t>
+          <t>I=0.030, p=0.188</t>
         </is>
       </c>
     </row>
